--- a/Plantilla_Asignaciones.xlsx
+++ b/Plantilla_Asignaciones.xlsx
@@ -483,13 +483,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -502,7 +503,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Columnas requeridas: Cedula, Nombre Estudiante, Formador 1, Formador 2 (opcional)</t>
+          <t>Columnas: Cedula, Nombre Estudiante, Formador 1, Formador 2, Correo (opcional)</t>
         </is>
       </c>
     </row>
@@ -528,6 +529,11 @@
           <t>FORMADOR 2</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -550,6 +556,11 @@
           <t>Jimmy</t>
         </is>
       </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>allison.rodriguez@uniminuto.edu.co</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -572,6 +583,11 @@
           <t>Paola</t>
         </is>
       </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>adriana.melo@uniminuto.edu.co</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -594,6 +610,7 @@
           <t>Estefania</t>
         </is>
       </c>
+      <c r="E7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -616,6 +633,11 @@
           <t>Erika Velosa</t>
         </is>
       </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>andrea.fino@uniminuto.edu.co</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -638,19 +660,20 @@
           <t>Paola</t>
         </is>
       </c>
+      <c r="E9" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>NOTA: Los nombres de los formadores deben coincidir exactamente con los registrados en el sistema.</t>
+          <t>NOTA: Los nombres de los formadores deben coincidir con los del sistema. La columna CORREO es opcional.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
